--- a/04_DESIGN_TABLES/DesignTable_6801_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6801_SW2.xlsx
@@ -885,13 +885,13 @@
         <v>0.375</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -1096,13 +1096,13 @@
         <v>0.22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         <v>0.22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.12702</v>
+        <v>0.12652</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
@@ -1518,13 +1518,13 @@
         <v>0.28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
@@ -1729,13 +1729,13 @@
         <v>0.28</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
@@ -1940,13 +1940,13 @@
         <v>0.375</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
@@ -2151,13 +2151,13 @@
         <v>0.44</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
@@ -2362,13 +2362,13 @@
         <v>0.28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
@@ -2573,13 +2573,13 @@
         <v>0.28</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
@@ -2784,13 +2784,13 @@
         <v>0.28125</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
@@ -2995,13 +2995,13 @@
         <v>0.28125</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
@@ -3206,13 +3206,13 @@
         <v>0.28125</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.16238</v>
+        <v>0.16188</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.32476</v>
+        <v>0.32426</v>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
@@ -3417,13 +3417,13 @@
         <v>0.375</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
@@ -3628,13 +3628,13 @@
         <v>0.44</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
@@ -3839,13 +3839,13 @@
         <v>0.53</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0.375</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
@@ -4261,13 +4261,13 @@
         <v>0.44</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
@@ -4472,13 +4472,13 @@
         <v>0.53</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
@@ -4683,13 +4683,13 @@
         <v>0.44</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
@@ -4894,13 +4894,13 @@
         <v>0.44</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
@@ -5105,13 +5105,13 @@
         <v>0.44</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.25403</v>
+        <v>0.25353</v>
       </c>
       <c r="BB22" t="n">
-        <v>0.50807</v>
+        <v>0.50757</v>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
@@ -5316,13 +5316,13 @@
         <v>0.53</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.306</v>
+        <v>0.3055</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.61199</v>
+        <v>0.61149</v>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
@@ -5527,13 +5527,13 @@
         <v>0.53125</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
@@ -5738,13 +5738,13 @@
         <v>0.53125</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
@@ -5949,13 +5949,13 @@
         <v>0.53125</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.30672</v>
+        <v>0.30622</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.61343</v>
+        <v>0.61293</v>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
@@ -6160,13 +6160,13 @@
         <v>0.655</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.37816</v>
+        <v>0.37766</v>
       </c>
       <c r="BB27" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.75583</v>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
@@ -6371,13 +6371,13 @@
         <v>0.65625</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.37889</v>
+        <v>0.37839</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.7577700000000001</v>
+        <v>0.75727</v>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
@@ -6582,13 +6582,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BB29" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
@@ -6793,13 +6793,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BB30" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
@@ -7004,13 +7004,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.47054</v>
+        <v>0.47004</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.94108</v>
+        <v>0.94058</v>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
@@ -7215,13 +7215,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.08542</v>
+        <v>1.08492</v>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
@@ -7426,13 +7426,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.08542</v>
+        <v>1.08492</v>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
@@ -7637,13 +7637,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.54271</v>
+        <v>0.54221</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.08542</v>
+        <v>1.08492</v>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
@@ -7848,13 +7848,13 @@
         <v>1.25</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.44338</v>
+        <v>1.44288</v>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
@@ -8059,13 +8059,13 @@
         <v>1.25</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.7216900000000001</v>
+        <v>0.72119</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.44338</v>
+        <v>1.44288</v>
       </c>
       <c r="BC36" t="inlineStr">
         <is>

--- a/04_DESIGN_TABLES/DesignTable_6801_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6801_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK36"/>
+  <dimension ref="A1:BK40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6428,14 +6428,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6801-16-20-NWO-FG</t>
+          <t>6801-16-10-NWO-FG</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="D29" t="n">
         <v>0.65625</v>
@@ -6462,70 +6462,70 @@
         <v>37</v>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="N29" t="n">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="O29" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0.027</v>
+        <v>0.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.945</v>
+        <v>0.505</v>
       </c>
       <c r="R29" t="n">
         <v>75</v>
       </c>
       <c r="S29" t="n">
-        <v>1.09542</v>
+        <v>0.58735</v>
       </c>
       <c r="T29" t="n">
         <v>75</v>
       </c>
       <c r="U29" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0.945</v>
+        <v>0.505</v>
       </c>
       <c r="W29" t="n">
-        <v>1.0825</v>
+        <v>0.5775</v>
       </c>
       <c r="X29" t="n">
         <v>0.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.3865</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.8125</v>
+        <v>0.4375</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.88</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.84</v>
+        <v>0.844</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.08</v>
+        <v>0.484</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AH29" t="n">
         <v>1.3125</v>
@@ -6546,58 +6546,58 @@
         <v>0.08333</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.625</v>
+        <v>0.875</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.469</v>
+        <v>0.391</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.099</v>
+        <v>0.899</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BB29" t="n">
-        <v>0.94058</v>
+        <v>0.75727</v>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>6801-16-20-NWO-FG</t>
+          <t>6801-16-10-NWO-FG</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 JIC x 1 5/8-12 (adjustable male ORB)</t>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 JIC x 7/8-14 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>1 5/8-12 (adjustable male ORB)</t>
+          <t>7/8-14 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -6622,49 +6622,49 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): legs / locknut hex / bores / flats from the Brennan TFA catalog p.41; JIC end MS33656J; adjustable ORB end data from the table's own -10 ORB rows (A5) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs)</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.41 alone; JIC end chain + ORB end data from the libraries / same-ORB-size rows; marked DimSource BRENNAN | hex A/F raised from Air-Way 1.312 to 1.3125 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
-          <t>6801-16-20-NWO-FG</t>
+          <t>6801-16-10-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6801-20-16-NWO-FG</t>
+          <t>6801-16-12-NWO-FG</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="E30" t="n">
         <v>0.125</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="G30" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="J30" t="n">
         <v>60</v>
@@ -6673,28 +6673,28 @@
         <v>37</v>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="N30" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="O30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="P30" t="n">
         <v>0.027</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.755</v>
+        <v>0.63</v>
       </c>
       <c r="R30" t="n">
         <v>75</v>
       </c>
       <c r="S30" t="n">
-        <v>0.87603</v>
+        <v>0.73169</v>
       </c>
       <c r="T30" t="n">
         <v>75</v>
@@ -6703,49 +6703,49 @@
         <v>0.41</v>
       </c>
       <c r="V30" t="n">
-        <v>0.755</v>
+        <v>0.63</v>
       </c>
       <c r="W30" t="n">
-        <v>0.866</v>
+        <v>0.722</v>
       </c>
       <c r="X30" t="n">
         <v>0.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5975</v>
+        <v>0.4725</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AA30" t="n">
         <v>0.469</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
         <v>0.41</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AI30" t="n">
         <v>0.08333</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="AK30" t="n">
         <v>0.04511</v>
@@ -6757,7 +6757,7 @@
         <v>0.08333</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AO30" t="n">
         <v>0.08333</v>
@@ -6775,40 +6775,40 @@
         <v>0.08333</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.102</v>
+        <v>0.899</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BB30" t="n">
-        <v>0.94058</v>
+        <v>0.75727</v>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>6801-20-16-NWO-FG</t>
+          <t>6801-16-12-NWO-FG</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 JIC x 1 5/16-12 (adjustable male ORB)</t>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 JIC x 1 1/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>1 5/16-12 (adjustable male ORB)</t>
+          <t>1 1/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -6833,49 +6833,49 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p041-t01: agrees on LEG_ORB@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
-          <t>6801-20-16-NWO-FG</t>
+          <t>6801-16-12-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6801-20-20-NWO-FG</t>
+          <t>6801-16-14-NWO-FG</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="E31" t="n">
         <v>0.125</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="G31" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="J31" t="n">
         <v>60</v>
@@ -6884,28 +6884,28 @@
         <v>37</v>
       </c>
       <c r="L31" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="N31" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="O31" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="P31" t="n">
         <v>0.027</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.945</v>
+        <v>0.695</v>
       </c>
       <c r="R31" t="n">
         <v>75</v>
       </c>
       <c r="S31" t="n">
-        <v>1.09542</v>
+        <v>0.80674</v>
       </c>
       <c r="T31" t="n">
         <v>75</v>
@@ -6914,49 +6914,49 @@
         <v>0.41</v>
       </c>
       <c r="V31" t="n">
-        <v>0.945</v>
+        <v>0.695</v>
       </c>
       <c r="W31" t="n">
-        <v>1.0825</v>
+        <v>0.7945</v>
       </c>
       <c r="X31" t="n">
         <v>0.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.535</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.8125</v>
+        <v>0.59375</v>
       </c>
       <c r="AA31" t="n">
         <v>0.469</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.88</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
         <v>0.41</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.08</v>
+        <v>0.72</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AI31" t="n">
         <v>0.08333</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="AK31" t="n">
         <v>0.04511</v>
@@ -6968,7 +6968,7 @@
         <v>0.08333</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.625</v>
+        <v>1.1875</v>
       </c>
       <c r="AO31" t="n">
         <v>0.08333</v>
@@ -6986,40 +6986,40 @@
         <v>0.08333</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.102</v>
+        <v>0.899</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.94058</v>
+        <v>0.75727</v>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>6801-20-20-NWO-FG</t>
+          <t>6801-16-14-NWO-FG</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 JIC x 1 5/8-12 (adjustable male ORB)</t>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 JIC x 1 3/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>1 5/8-12 (adjustable male ORB)</t>
+          <t>1 3/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -7044,49 +7044,49 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | Brennan 6801-20-20-NWO-FG STEP (2026-09-25): JIC leg 2.060, ORB leg 2.250, tip to body face 1.140, ORB thread 0.469, nut hex 1.875, body hex 1.625, undercut dia 1.507 - all agree with Air-Way (within its 2-decimal rounding)</t>
+          <t>ORB -14 groove width UNPUBLISHED and unmeasured | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p041-t01: agrees on LEG_ORB@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BK31" t="inlineStr">
         <is>
-          <t>6801-20-20-NWO-FG</t>
+          <t>6801-16-14-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6801-20-24-NWO-FG</t>
+          <t>6801-16-16-NWO-FG</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="E32" t="n">
         <v>0.125</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="G32" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="J32" t="n">
         <v>60</v>
@@ -7095,28 +7095,28 @@
         <v>37</v>
       </c>
       <c r="L32" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>0.91</v>
       </c>
       <c r="O32" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="P32" t="n">
         <v>0.027</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.07</v>
+        <v>0.755</v>
       </c>
       <c r="R32" t="n">
         <v>75</v>
       </c>
       <c r="S32" t="n">
-        <v>1.23976</v>
+        <v>0.87603</v>
       </c>
       <c r="T32" t="n">
         <v>75</v>
@@ -7125,49 +7125,49 @@
         <v>0.41</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>0.755</v>
       </c>
       <c r="W32" t="n">
-        <v>1.227</v>
+        <v>0.866</v>
       </c>
       <c r="X32" t="n">
         <v>0.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.878</v>
+        <v>0.5975</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AA32" t="n">
         <v>0.469</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="AC32" t="n">
         <v>0.41</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.31</v>
+        <v>0.84</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AI32" t="n">
         <v>0.08333</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="AK32" t="n">
         <v>0.04511</v>
@@ -7179,7 +7179,7 @@
         <v>0.08333</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="AO32" t="n">
         <v>0.08333</v>
@@ -7197,40 +7197,40 @@
         <v>0.08333</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.88</v>
+        <v>1.3125</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.242</v>
+        <v>0.899</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.88</v>
+        <v>1.3125</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.25</v>
+        <v>0.91</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.54221</v>
+        <v>0.37839</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.54221</v>
+        <v>0.37839</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.08492</v>
+        <v>0.75727</v>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>6801-20-24-NWO-FG</t>
+          <t>6801-16-16-NWO-FG</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 JIC x 1 7/8-12 (adjustable male ORB)</t>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 JIC x 1 5/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>1 7/8-12 (adjustable male ORB)</t>
+          <t>1 5/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
@@ -7260,44 +7260,44 @@
       </c>
       <c r="BJ32" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs)</t>
+          <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p041-t01: agrees on LEG_ORB@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>6801-20-24-NWO-FG</t>
+          <t>6801-16-16-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6801-24-20-NWO-FG</t>
+          <t>6801-16-20-NWO-FG</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="E33" t="n">
         <v>0.125</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5454</v>
+        <v>0.4365</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1298</v>
+        <v>0.1292</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2482</v>
+        <v>0.1858</v>
       </c>
       <c r="J33" t="n">
         <v>60</v>
@@ -7306,13 +7306,13 @@
         <v>37</v>
       </c>
       <c r="L33" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="O33" t="n">
         <v>0.75</v>
@@ -7360,25 +7360,25 @@
         <v>0.41</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.31</v>
+        <v>0.84</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="AF33" t="n">
         <v>1.08</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="AI33" t="n">
         <v>0.08333</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.5454</v>
+        <v>0.4365</v>
       </c>
       <c r="AK33" t="n">
         <v>0.04511</v>
@@ -7408,40 +7408,40 @@
         <v>0.08333</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.247</v>
+        <v>1.099</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.54221</v>
+        <v>0.47004</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.54221</v>
+        <v>0.47004</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.08492</v>
+        <v>0.94058</v>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>6801-24-20-NWO-FG</t>
+          <t>6801-16-20-NWO-FG</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 7/8-12 JIC x 1 5/8-12 (adjustable male ORB)</t>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/16-12 JIC x 1 5/8-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>1 7/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
@@ -7476,39 +7476,39 @@
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>6801-24-20-NWO-FG</t>
+          <t>6801-16-20-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6801-24-24-NWO-FG</t>
+          <t>6801-20-16-NWO-FG</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="E34" t="n">
         <v>0.125</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="J34" t="n">
         <v>60</v>
@@ -7517,28 +7517,28 @@
         <v>37</v>
       </c>
       <c r="L34" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="O34" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="P34" t="n">
         <v>0.027</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.07</v>
+        <v>0.755</v>
       </c>
       <c r="R34" t="n">
         <v>75</v>
       </c>
       <c r="S34" t="n">
-        <v>1.23976</v>
+        <v>0.87603</v>
       </c>
       <c r="T34" t="n">
         <v>75</v>
@@ -7547,49 +7547,49 @@
         <v>0.41</v>
       </c>
       <c r="V34" t="n">
-        <v>1.07</v>
+        <v>0.755</v>
       </c>
       <c r="W34" t="n">
-        <v>1.227</v>
+        <v>0.866</v>
       </c>
       <c r="X34" t="n">
         <v>0.05</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.878</v>
+        <v>0.5975</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.9375</v>
+        <v>0.65625</v>
       </c>
       <c r="AA34" t="n">
         <v>0.469</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="AC34" t="n">
         <v>0.41</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.31</v>
+        <v>0.84</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="AI34" t="n">
         <v>0.08333</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="AK34" t="n">
         <v>0.04511</v>
@@ -7601,7 +7601,7 @@
         <v>0.08333</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.875</v>
+        <v>1.3125</v>
       </c>
       <c r="AO34" t="n">
         <v>0.08333</v>
@@ -7619,40 +7619,40 @@
         <v>0.08333</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.247</v>
+        <v>1.102</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.54221</v>
+        <v>0.47004</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.54221</v>
+        <v>0.47004</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.08492</v>
+        <v>0.94058</v>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>6801-24-24-NWO-FG</t>
+          <t>6801-20-16-NWO-FG</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 7/8-12 JIC x 1 7/8-12 (adjustable male ORB)</t>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 JIC x 1 5/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>1 7/8-12 JIC</t>
+          <t>1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>1 7/8-12 (adjustable male ORB)</t>
+          <t>1 5/16-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
@@ -7682,44 +7682,44 @@
       </c>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | Brennan 6801-24-24-NWO-FG STEP (2026-09-25): JIC leg 2.330, ORB leg 2.390, tip to body face 1.140, ORB thread 0.469, nut hex 2.125, body hex 1.875, undercut dia 1.756 - all agree with Air-Way (within its 2-decimal rounding)</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs)</t>
         </is>
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>6801-24-24-NWO-FG</t>
+          <t>6801-20-16-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6801-24-32-NWO-FG</t>
+          <t>6801-20-20-NWO-FG</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.81</v>
+        <v>2.06</v>
       </c>
       <c r="C35" t="n">
-        <v>1.25</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="E35" t="n">
         <v>0.125</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="J35" t="n">
         <v>60</v>
@@ -7728,28 +7728,28 @@
         <v>37</v>
       </c>
       <c r="L35" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>1.25</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="O35" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="P35" t="n">
         <v>0.027</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.38</v>
+        <v>0.945</v>
       </c>
       <c r="R35" t="n">
         <v>75</v>
       </c>
       <c r="S35" t="n">
-        <v>1.59771</v>
+        <v>1.09542</v>
       </c>
       <c r="T35" t="n">
         <v>75</v>
@@ -7758,49 +7758,49 @@
         <v>0.41</v>
       </c>
       <c r="V35" t="n">
-        <v>1.38</v>
+        <v>0.945</v>
       </c>
       <c r="W35" t="n">
-        <v>1.58</v>
+        <v>1.0825</v>
       </c>
       <c r="X35" t="n">
         <v>0.05</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.1905</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="AA35" t="n">
         <v>0.469</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC35" t="n">
         <v>0.41</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.312</v>
+        <v>1.08</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.81</v>
+        <v>2.06</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.781</v>
+        <v>1.08</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="AI35" t="n">
         <v>0.08333</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="AK35" t="n">
         <v>0.04511</v>
@@ -7812,7 +7812,7 @@
         <v>0.08333</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="AO35" t="n">
         <v>0.08333</v>
@@ -7830,40 +7830,40 @@
         <v>0.08333</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.727</v>
+        <v>1.102</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.25</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.25</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.72119</v>
+        <v>0.47004</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.72119</v>
+        <v>0.47004</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.44288</v>
+        <v>0.94058</v>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>6801-24-32-NWO-FG</t>
+          <t>6801-20-20-NWO-FG</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 7/8-12 JIC x 2 1/2-12 (adjustable male ORB)</t>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 JIC x 1 5/8-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>1 7/8-12 JIC</t>
+          <t>1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>2 1/2-12 (adjustable male ORB)</t>
+          <t>1 5/8-12 (adjustable male ORB)</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
@@ -7888,49 +7888,49 @@
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-02 (batch 15): the dimension cells MEASURED on the part's own Brennan STEP 09_STEP_FILES/BRENNAN_6801-24-32-NWO-FG.stp (sha256 a1ca760c7e23..., received 2026-10-02, tools/_out/step_ingest_20261002/MANIFEST_sha256.txt) with tools/measure/nwo.py (the adjustable-ORB walk / parse of 2026-09-25) for the ORB end and the fix2702 measure_bh reading for the JIC leg and the bores (tools/_out/batch15_20261002/work/FG-STEP/scripts/measure_6801.py; method validated first on the 12 Brennan 6801 STEPs of accepted sizes: every cell = the review row within rounding except the two known findings 6801-04-02 LEG_ORB and 6801-12-12 ORB_THDL; work/FG-STEP/measure/measure_6801.txt): LEG_JIC 2.810 (crossing to the JIC tip), LEG_ORB 2.890 (crossing to the ORB tip), ORB_I3 1.140 (ORB tip to the body face), ORB_THDL 0.469 (ORB thread length, tip to the undercut), ORB_GRVDIA 2.381 (undercut root dia), HEXB 2.750 (locknut across flats), Y 2.500 (body hex flats), D1 1.312 (JIC bore), D2 1.781 (ORB bore); THDMAJ_A 1.875 / THDMAJ_B 2.5 = the -24 JIC / -32 ORB dash of the part number (STEP thread majors 1.875 / 2.5; OMi Items row 2189 Side 1 / 2 Thread); JIC_RELIEFL / RELIEFANG / JIC_THDZ / JIC_CONEDIA / JIC_LANDL / JIC_SEATL / SEATB = the -24 MS33656J chain of the generator JIC library (gen_straight2.JIC[24], 2403 table VERIFIED vs Brennan) = every -24 JIC row of this table (gen_tee builds the JIC end from that library) [standing user decision: a forged -FG part may be built from its own Brennan STEP; one manufacturer -&gt; ASSUMED]. The adjustable ORB end of this STEP (neck 1.1 x 0.027, locknut 0.41 thick, washer 1.58 x 0.05, undercut 0.184 long; ORB_I3 / ORB_THDL / ORB_GRVDIA as above) = gen_tee NWO_MEAS[-32] (Brennan 6801-32-32-NWO-FG) and the table's other -32 ORB rows exactly. ORB_GRVW left EMPTY (no source): Parker ORD-5700 Table 4-4 prints no groove width G on the -32 row (07_RAW_EXTRACTS/Report_ORB_groove_ORD5700.md: G not printed for 3-914..3-932), the table title lists "ORB -14/-32 groove width" as a remaining block, and no -32 ORB row of this table carries one - the accepted 6801-32-32-NWO-FG row is empty for the same reason ($COMMENT "ORB -32 groove width UNPUBLISHED and unmeasured"). The only -32 value on file, 0.125 in gen_straight2.ORB[32], was measured on a different part (the fixed-ORB Brennan 6400-32-32-O STEP); using it here would be a transfer from another part that no user decision covers. The row is still ASSUMED: gen_tee does not read ORB_GRVW and it is not in the SW2 table, so every value the model uses has a source; the empty cell keeps the groove width itself unsourced, as on the accepted -32 row. The Brennan TFA catalog p41 (table TFA-p041-t01) (page-verified; tools/_out/brennan_catalog_20261001/catalog_verified.json) prints M 2.810, M7 2.890, C HEX 2.750, Y FLATS 2.500, B1 / B2 DRILL 1.312 / 1.781, B1 1-7/8-12, B2 2-1/2-12 = the STEP (same manufacturer, not an independent source). The OMi dimension file gives no dimension for this SKU (07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items row 2189: threads only); Air-Way prints no row for this -FG part. Where the MODEL text below or a generator warning says Air-Way (legs, ORB_I3, locknut hex HEXB, groove / undercut dia, thread length, hex), this row uses these STEP values | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-02 (resolved, batch 15): built from its OWN Brennan STEP (09_STEP_FILES/BRENNAN_6801-24-32-NWO-FG.stp; one manufacturer -&gt; ASSUMED); every measured cell equals the Brennan TFA catalog p41 row (same source); ORB -32 groove width UNPUBLISHED and unmeasured (ORB_GRVW empty, as on 6801-32-32-NWO-FG)</t>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | Brennan 6801-20-20-NWO-FG STEP (2026-09-25): JIC leg 2.060, ORB leg 2.250, tip to body face 1.140, ORB thread 0.469, nut hex 1.875, body hex 1.625, undercut dia 1.507 - all agree with Air-Way (within its 2-decimal rounding)</t>
         </is>
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>6801-24-32-NWO-FG</t>
+          <t>6801-20-20-NWO-FG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6801-32-32-NWO-FG</t>
+          <t>6801-20-24-NWO-FG</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.06</v>
+        <v>2.2</v>
       </c>
       <c r="C36" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>1.25</v>
+        <v>0.8125</v>
       </c>
       <c r="E36" t="n">
         <v>0.125</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7124</v>
+        <v>0.4316</v>
       </c>
       <c r="G36" t="n">
-        <v>1.19</v>
+        <v>0.753</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1292</v>
+        <v>0.1288</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3318</v>
+        <v>0.2382</v>
       </c>
       <c r="J36" t="n">
         <v>60</v>
@@ -7939,28 +7939,28 @@
         <v>37</v>
       </c>
       <c r="L36" t="n">
-        <v>2.89</v>
+        <v>2.39</v>
       </c>
       <c r="M36" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N36" t="n">
         <v>1.25</v>
       </c>
-      <c r="N36" t="n">
-        <v>1.75</v>
-      </c>
       <c r="O36" t="n">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="P36" t="n">
         <v>0.027</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="R36" t="n">
         <v>75</v>
       </c>
       <c r="S36" t="n">
-        <v>1.59771</v>
+        <v>1.23976</v>
       </c>
       <c r="T36" t="n">
         <v>75</v>
@@ -7969,49 +7969,49 @@
         <v>0.41</v>
       </c>
       <c r="V36" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="W36" t="n">
-        <v>1.58</v>
+        <v>1.227</v>
       </c>
       <c r="X36" t="n">
         <v>0.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.1905</v>
+        <v>0.878</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="AA36" t="n">
         <v>0.469</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="AC36" t="n">
         <v>0.41</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.78</v>
+        <v>1.08</v>
       </c>
       <c r="AE36" t="n">
-        <v>3.06</v>
+        <v>2.2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.89</v>
+        <v>2.39</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.5</v>
+        <v>1.625</v>
       </c>
       <c r="AI36" t="n">
         <v>0.08333</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.7124</v>
+        <v>0.4316</v>
       </c>
       <c r="AK36" t="n">
         <v>0.04511</v>
@@ -8023,7 +8023,7 @@
         <v>0.08333</v>
       </c>
       <c r="AN36" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="AO36" t="n">
         <v>0.08333</v>
@@ -8041,73 +8041,917 @@
         <v>0.08333</v>
       </c>
       <c r="AT36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.242</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.08492</v>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>6801-20-24-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 5/8-12 JIC x 1 7/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>6801</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>1 5/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BG36" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BJ36" t="inlineStr">
+        <is>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs)</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>6801-20-24-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>6801-24-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="J37" t="n">
+        <v>60</v>
+      </c>
+      <c r="K37" t="n">
+        <v>37</v>
+      </c>
+      <c r="L37" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="R37" t="n">
+        <v>75</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.09542</v>
+      </c>
+      <c r="T37" t="n">
+        <v>75</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.0825</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.08492</v>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>6801-24-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 7/8-12 JIC x 1 5/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>6801</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs)</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>6801-24-20-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>6801-24-24-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="J38" t="n">
+        <v>60</v>
+      </c>
+      <c r="K38" t="n">
+        <v>37</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R38" t="n">
+        <v>75</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.23976</v>
+      </c>
+      <c r="T38" t="n">
+        <v>75</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.08492</v>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>6801-24-24-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 7/8-12 JIC x 1 7/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>6801</t>
+        </is>
+      </c>
+      <c r="BF38" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 + GRVW measured (Brennan 6400); legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>DataStatus ASSUMED (hex/legs single-source for unequal-dash) -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | Brennan 6801-24-24-NWO-FG STEP (2026-09-25): JIC leg 2.330, ORB leg 2.390, tip to body face 1.140, ORB thread 0.469, nut hex 2.125, body hex 1.875, undercut dia 1.756 - all agree with Air-Way (within its 2-decimal rounding)</t>
+        </is>
+      </c>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>6801-24-24-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6801-24-32-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="J39" t="n">
+        <v>60</v>
+      </c>
+      <c r="K39" t="n">
+        <v>37</v>
+      </c>
+      <c r="L39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R39" t="n">
+        <v>75</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.59771</v>
+      </c>
+      <c r="T39" t="n">
+        <v>75</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.5454</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN39" t="n">
         <v>2.5</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AO39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU39" t="n">
         <v>1.727</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AV39" t="n">
         <v>2.5</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AW39" t="n">
         <v>1.75</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AX39" t="n">
         <v>1.25</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="AY39" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ36" t="n">
+      <c r="AZ39" t="n">
         <v>0.72119</v>
       </c>
-      <c r="BA36" t="n">
+      <c r="BA39" t="n">
         <v>0.72119</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BB39" t="n">
         <v>1.44288</v>
       </c>
-      <c r="BC36" t="inlineStr">
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>6801-24-32-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>90 deg Male JIC x Adjustable Male ORB Elbow, 1 7/8-12 JIC x 2 1/2-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>6801</t>
+        </is>
+      </c>
+      <c r="BF39" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-02 (batch 15): the dimension cells MEASURED on the part's own Brennan STEP 09_STEP_FILES/BRENNAN_6801-24-32-NWO-FG.stp (sha256 a1ca760c7e23..., received 2026-10-02, tools/_out/step_ingest_20261002/MANIFEST_sha256.txt) with tools/measure/nwo.py (the adjustable-ORB walk / parse of 2026-09-25) for the ORB end and the fix2702 measure_bh reading for the JIC leg and the bores (tools/_out/batch15_20261002/work/FG-STEP/scripts/measure_6801.py; method validated first on the 12 Brennan 6801 STEPs of accepted sizes: every cell = the review row within rounding except the two known findings 6801-04-02 LEG_ORB and 6801-12-12 ORB_THDL; work/FG-STEP/measure/measure_6801.txt): LEG_JIC 2.810 (crossing to the JIC tip), LEG_ORB 2.890 (crossing to the ORB tip), ORB_I3 1.140 (ORB tip to the body face), ORB_THDL 0.469 (ORB thread length, tip to the undercut), ORB_GRVDIA 2.381 (undercut root dia), HEXB 2.750 (locknut across flats), Y 2.500 (body hex flats), D1 1.312 (JIC bore), D2 1.781 (ORB bore); THDMAJ_A 1.875 / THDMAJ_B 2.5 = the -24 JIC / -32 ORB dash of the part number (STEP thread majors 1.875 / 2.5; OMi Items row 2189 Side 1 / 2 Thread); JIC_RELIEFL / RELIEFANG / JIC_THDZ / JIC_CONEDIA / JIC_LANDL / JIC_SEATL / SEATB = the -24 MS33656J chain of the generator JIC library (gen_straight2.JIC[24], 2403 table VERIFIED vs Brennan) = every -24 JIC row of this table (gen_tee builds the JIC end from that library) [standing user decision: a forged -FG part may be built from its own Brennan STEP; one manufacturer -&gt; ASSUMED]. The adjustable ORB end of this STEP (neck 1.1 x 0.027, locknut 0.41 thick, washer 1.58 x 0.05, undercut 0.184 long; ORB_I3 / ORB_THDL / ORB_GRVDIA as above) = gen_tee NWO_MEAS[-32] (Brennan 6801-32-32-NWO-FG) and the table's other -32 ORB rows exactly. ORB_GRVW left EMPTY (no source): Parker ORD-5700 Table 4-4 prints no groove width G on the -32 row (07_RAW_EXTRACTS/Report_ORB_groove_ORD5700.md: G not printed for 3-914..3-932), the table title lists "ORB -14/-32 groove width" as a remaining block, and no -32 ORB row of this table carries one - the accepted 6801-32-32-NWO-FG row is empty for the same reason ($COMMENT "ORB -32 groove width UNPUBLISHED and unmeasured"). The only -32 value on file, 0.125 in gen_straight2.ORB[32], was measured on a different part (the fixed-ORB Brennan 6400-32-32-O STEP); using it here would be a transfer from another part that no user decision covers. The row is still ASSUMED: gen_tee does not read ORB_GRVW and it is not in the SW2 table, so every value the model uses has a source; the empty cell keeps the groove width itself unsourced, as on the accepted -32 row. The Brennan TFA catalog p41 (table TFA-p041-t01) (page-verified; tools/_out/brennan_catalog_20261001/catalog_verified.json) prints M 2.810, M7 2.890, C HEX 2.750, Y FLATS 2.500, B1 / B2 DRILL 1.312 / 1.781, B1 1-7/8-12, B2 2-1/2-12 = the STEP (same manufacturer, not an independent source). The OMi dimension file gives no dimension for this SKU (07_RAW_EXTRACTS/omi_dimensions/WebsitePartsInfo2026.xlsx Items row 2189: threads only); Air-Way prints no row for this -FG part. Where the MODEL text below or a generator warning says Air-Way (legs, ORB_I3, locknut hex HEXB, groove / undercut dia, thread length, hex), this row uses these STEP values | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BJ39" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-02 (resolved, batch 15): built from its OWN Brennan STEP (09_STEP_FILES/BRENNAN_6801-24-32-NWO-FG.stp; one manufacturer -&gt; ASSUMED); every measured cell equals the Brennan TFA catalog p41 row (same source); ORB -32 groove width UNPUBLISHED and unmeasured (ORB_GRVW empty, as on 6801-32-32-NWO-FG)</t>
+        </is>
+      </c>
+      <c r="BK39" t="inlineStr">
+        <is>
+          <t>6801-24-32-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>6801-32-32-NWO-FG</t>
         </is>
       </c>
-      <c r="BD36" t="inlineStr">
+      <c r="B40" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="J40" t="n">
+        <v>60</v>
+      </c>
+      <c r="K40" t="n">
+        <v>37</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R40" t="n">
+        <v>75</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1.59771</v>
+      </c>
+      <c r="T40" t="n">
+        <v>75</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.1905</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.727</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.44288</v>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>6801-32-32-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
         <is>
           <t>90 deg Male JIC x Adjustable Male ORB Elbow, 2 1/2-12 JIC x 2 1/2-12 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BE36" t="inlineStr">
+      <c r="BE40" t="inlineStr">
         <is>
           <t>6801</t>
         </is>
       </c>
-      <c r="BF36" t="inlineStr">
+      <c r="BF40" t="inlineStr">
         <is>
           <t>2 1/2-12 JIC</t>
         </is>
       </c>
-      <c r="BG36" t="inlineStr">
+      <c r="BG40" t="inlineStr">
         <is>
           <t>2 1/2-12 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BH36" t="inlineStr">
+      <c r="BH40" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BI36" t="inlineStr">
+      <c r="BI40" t="inlineStr">
         <is>
           <t>JIC: MS33656J==Brennan VERIFIED; ORB thd: MS51527 J2; groove: ORD-5700 +; legs: Air-Way (MS51527 corroborates matched-dash) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BJ36" t="inlineStr">
+      <c r="BJ40" t="inlineStr">
         <is>
           <t>ORB -32 groove width UNPUBLISHED and unmeasured | Brennan 6801-32-32-NWO-FG STEP (2026-09-25): JIC leg 3.060, ORB leg 2.890, tip to body face 1.140, ORB thread 0.469, nut hex 2.750, body hex 2.500, undercut dia 2.381 - all agree with Air-Way (within its 2-decimal rounding)</t>
         </is>
       </c>
-      <c r="BK36" t="inlineStr">
+      <c r="BK40" t="inlineStr">
         <is>
           <t>6801-32-32-NWO-FG</t>
         </is>
